--- a/data/rules.xlsx
+++ b/data/rules.xlsx
@@ -4,29 +4,22 @@
   <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="0"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet r:id="rId1" sheetId="1" name="Lado 1"/>
     <sheet r:id="rId2" sheetId="2" name="Lado 2"/>
   </sheets>
   <definedNames>
-    <definedName name="Rules_1" localSheetId="0">'Lado 1'!$A$1:$C$4</definedName>
-    <definedName name="Rules_2" localSheetId="1">'Lado 2'!$A$1:$C$4</definedName>
+    <definedName name="Rules_1" localSheetId="0">='Lado 1'!$A$1:$C$3</definedName>
+    <definedName name="Rules_2" localSheetId="1">='Lado 2'!$A$1:$C$3</definedName>
   </definedNames>
   <calcPr fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="2">
-  <si>
-    <t xml:space="preserve">      </t>
-  </si>
-  <si>
-    <t xml:space="preserve">       </t>
-  </si>
-</sst>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="0" uniqueCount="0"/>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -49,7 +42,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -81,15 +74,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
@@ -397,15 +387,15 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="4" width="6.719285714285714" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="4" width="6.719285714285714" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="4" width="10.862142857142858" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="3" width="6.719285714285714" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="3" width="6.719285714285714" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="3" width="10.862142857142858" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="19.5">
       <c r="A1" s="2">
         <v>1</v>
       </c>
@@ -416,7 +406,7 @@
         <v>1</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -424,29 +414,18 @@
         <v>2</v>
       </c>
       <c r="C2" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
+        <v>10</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
       <c r="A3" s="2">
         <v>1</v>
       </c>
       <c r="B3" s="2">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C3" s="2">
-        <v>3</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
-      <c r="A4" s="2">
-        <v>4</v>
-      </c>
-      <c r="B4" s="2">
-        <v>4</v>
-      </c>
-      <c r="C4" s="2">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -459,12 +438,12 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="4" width="9.005" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="4" width="11.005" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="4" width="14.005" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="3" width="9.005" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="3" width="11.005" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="3" width="14.005" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
@@ -485,30 +464,19 @@
       <c r="B2" s="2">
         <v>2</v>
       </c>
-      <c r="C2" s="3" t="s">
-        <v>0</v>
+      <c r="C2" s="2">
+        <v>20</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
       <c r="A3" s="2">
         <v>1</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
-      <c r="A4" s="2">
-        <v>5</v>
-      </c>
-      <c r="B4" s="2">
-        <v>5</v>
-      </c>
-      <c r="C4" s="2">
-        <v>5</v>
+      <c r="B3" s="2">
+        <v>20</v>
+      </c>
+      <c r="C3" s="2">
+        <v>21</v>
       </c>
     </row>
   </sheetData>

--- a/data/rules.xlsx
+++ b/data/rules.xlsx
@@ -11,8 +11,8 @@
     <sheet r:id="rId2" sheetId="2" name="Lado 2"/>
   </sheets>
   <definedNames>
-    <definedName name="Rules_1" localSheetId="0">='Lado 1'!$A$1:$C$3</definedName>
-    <definedName name="Rules_2" localSheetId="1">='Lado 2'!$A$1:$C$3</definedName>
+    <definedName name="Rules_1" localSheetId="0">='Lado 1'!$A$1:$C$4</definedName>
+    <definedName name="Rules_2" localSheetId="1">='Lado 2'!$A$1:$C$4</definedName>
   </definedNames>
   <calcPr fullCalcOnLoad="1"/>
 </workbook>
@@ -74,12 +74,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
@@ -387,7 +390,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" style="3" width="6.719285714285714" customWidth="1" bestFit="1"/>
@@ -414,18 +417,29 @@
         <v>2</v>
       </c>
       <c r="C2" s="2">
-        <v>10</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
+        <v>100</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
       <c r="A3" s="2">
         <v>1</v>
       </c>
       <c r="B3" s="2">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="C3" s="2">
-        <v>11</v>
+        <v>1000</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
+      <c r="A4" s="4">
+        <v>4</v>
+      </c>
+      <c r="B4" s="4">
+        <v>4</v>
+      </c>
+      <c r="C4" s="4">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -438,7 +452,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" style="3" width="9.005" customWidth="1" bestFit="1"/>
@@ -446,7 +460,7 @@
     <col min="3" max="3" style="3" width="14.005" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="19.5">
       <c r="A1" s="1">
         <v>1</v>
       </c>
@@ -457,7 +471,7 @@
         <v>1</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -465,7 +479,7 @@
         <v>2</v>
       </c>
       <c r="C2" s="2">
-        <v>20</v>
+        <v>200</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
@@ -473,10 +487,21 @@
         <v>1</v>
       </c>
       <c r="B3" s="2">
-        <v>20</v>
+        <v>200</v>
       </c>
       <c r="C3" s="2">
-        <v>21</v>
+        <v>2000</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
+      <c r="A4" s="2">
+        <v>5</v>
+      </c>
+      <c r="B4" s="2">
+        <v>5</v>
+      </c>
+      <c r="C4" s="2">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
